--- a/docs/TEST/04_FAN_F系统测试报告.xlsx
+++ b/docs/TEST/04_FAN_F系统测试报告.xlsx
@@ -146,18 +146,16 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -544,298 +542,429 @@
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>1、 测试范围</t>
         </is>
       </c>
     </row>
+    <row r="3" ht="23" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+    </row>
     <row r="4" ht="23" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>类别</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>结果</t>
-        </is>
-      </c>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CAN/ISO-TP</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>全部通过</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
     </row>
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>CAN/ISO-TP</t>
+          <t>UDS</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>全部通过</t>
         </is>
       </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
     </row>
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>UDS</t>
+          <t>安全访问</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
           <t>全部通过</t>
         </is>
       </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
     </row>
     <row r="7" ht="23" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>安全访问</t>
+          <t>系统检查</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t>全部通过</t>
         </is>
       </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
     </row>
     <row r="8" ht="23" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>系统检查</t>
+          <t>OTA</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>全部通过</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="23" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>OTA</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>全部通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2 测试制品</t>
         </is>
       </c>
+    </row>
+    <row r="10" ht="23" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>制品</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="23" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>FAN_F_ECU_TEST.hex</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
     </row>
     <row r="12" ht="23" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>制品</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
+          <t>FAN_CAN_APP_SAFE_RAMP_UNIVERSAL.hex</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
     </row>
     <row r="13" ht="23" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>FAN_F_ECU_TEST.hex</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>rfd1_nxp_sdk_ref_NONPROD_TEST_ONLY.pkg</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
     </row>
     <row r="14" ht="23" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>FAN_CAN_APP_SAFE_RAMP_UNIVERSAL.hex</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="23" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>rfd1_nxp_sdk_ref_NONPROD_TEST_ONLY.pkg</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>FAN_F_CAN_Tester.exe</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>3 CAN通信记录</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>FAN_F_CAN_Tester.exe</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>3 CAN通信记录</t>
-        </is>
-      </c>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="23" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>总帧数</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>12290</v>
+      </c>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="23" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>11789</v>
+      </c>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
     </row>
     <row r="19" ht="23" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>结果</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>501</v>
+      </c>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
     </row>
     <row r="20" ht="23" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>总帧数</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>12290</v>
-      </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
+          <t>CAN ID数量</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
     </row>
     <row r="21" ht="23" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>11789</v>
-      </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="23" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>RX</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>501</v>
-      </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+          <t>CAN周期</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>count=5, min=483ms, max=541ms, expected=500±100ms</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>5 产品身份DID测试结果</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="23" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>CAN ID数量</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>用例</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>DID</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>ASCII</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>响应</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="23" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>CAN周期</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>count=5, min=483ms, max=541ms, expected=500±100ms</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5 产品身份DID测试结果</t>
+          <t>UDS-018</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>F187双通道精确值读取</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>A61300000859 + 0x20</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>62 F1 87 41 36 31 33 30 30 30 30 30 38 35 39 20</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="23" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>UDS-019</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>F189双通道精确值读取</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>A6130A14A8S001001</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>62 F1 89 41 36 31 33 30 41 31 34 41 38 53 30 30 31 30 30 31</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="23" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>UDS-020</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>F18A双通道精确值读取</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>A1448</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>62 F1 8A 41 31 34 34 38</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>用例</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>DID</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>ASCII</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>响应</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>结果</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>UDS-021</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>F191双通道精确值读取</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>A6130A1448H001001</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>62 F1 91 41 36 31 33 30 41 31 34 34 38 48 30 30 31 30 30 31</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>UDS-018</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>F187双通道精确值读取</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>A61300000859 + 0x20</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>62 F1 87 41 36 31 33 30 30 30 30 30 38 35 39 20</t>
+          <t>UDS-022</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>F197双通道精确值读取</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>FAN_F + 9个空格</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>62 F1 97 46 41 4E 5F 46 20 20 20 20 20 20 20 20 20</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -844,174 +973,205 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="23" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>UDS-019</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>F189双通道精确值读取</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>A6130A14A8S001001</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>62 F1 89 41 36 31 33 30 41 31 34 41 38 53 30 30 31 30 30 31</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="23" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>UDS-020</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>F18A双通道精确值读取</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>A1448</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>62 F1 8A 41 31 34 34 38</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>上述5项均在OBD、OTA物理通道完成逐字节比较。F187末尾0x20和F197尾部空格计入长度及字节校验。F18F仍按未就绪状态处理，读取返回NRC 0x31。</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>6 全量测试结果</t>
         </is>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>UDS-021</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>F191双通道精确值读取</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>A6130A1448H001001</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>62 F1 91 41 36 31 33 30 41 31 34 34 38 48 30 30 31 30 30 31</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>测试项目</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>主要实测结果</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>结论</t>
         </is>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>UDS-022</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>F197双通道精确值读取</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>FAN_F + 9个空格</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
+          <t>CAN-001</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>CAN设备连接</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>CAN/ISO-TP</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>CAN Broker已连接</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="23" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>CAN-002</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>OBD/OTA双通道响应</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>CAN/ISO-TP</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>62 F1 97 46 41 4E 5F 46 20 20 20 20 20 20 20 20 20</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>上述5项均在OBD、OTA物理通道完成逐字节比较。F187末尾0x20和F197尾部空格计入长度及字节校验。F18F仍按未就绪状态处理，读取返回NRC 0x31。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>6 全量测试结果</t>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="23" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CAN-003</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>ISO-TP单帧</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>CAN/ISO-TP</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Boot诊断服务已在线</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="23" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>CAN-004</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>ISO-TP多帧</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>CAN/ISO-TP</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>62 F1 97 46 41 4E 5F 46 20 20 20 20 20 20 20 20 20</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>测试项目</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>类别</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>主要实测结果</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>结论</t>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>UDS-001</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Default会话</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>UDS</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Boot诊断服务已在线</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
         </is>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>CAN-001</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>CAN设备连接</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>CAN/ISO-TP</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>CAN Broker已连接</t>
+          <t>UDS-002</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Programming会话门禁</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>UDS</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>50 02 00 32 01 F4</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -1023,22 +1183,22 @@
     <row r="38" ht="23" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>CAN-002</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>OBD/OTA双通道响应</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>CAN/ISO-TP</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>62 F1 97 46 41 4E 5F 46 20 20 20 20 20 20 20 20 20</t>
+          <t>UDS-003</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Extended会话和P2/P2*</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>UDS</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>50 03 00 32 01 F4</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -1050,22 +1210,22 @@
     <row r="39" ht="23" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>CAN-003</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>ISO-TP单帧</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>CAN/ISO-TP</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Boot诊断服务已在线</t>
+          <t>UDS-004</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>S3超时回Default</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>UDS</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>S3超时后Boot已回到Default会话：7F 27 7E</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1077,22 +1237,22 @@
     <row r="40" ht="23" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>CAN-004</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>ISO-TP多帧</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>CAN/ISO-TP</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>62 F1 97 46 41 4E 5F 46 20 20 20 20 20 20 20 20 20</t>
+          <t>UDS-005</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>TesterPresent和抑制正响应</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>UDS</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>在200ms观察窗内无响应</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -1104,22 +1264,22 @@
     <row r="41" ht="23" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>UDS-001</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Default会话</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
+          <t>UDS-007</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>系统标识DID读取</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>UDS</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Boot诊断服务已在线</t>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>62 F1 97 46 41 4E 5F 46 20 20 20 20 20 20 20 20 20</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1131,22 +1291,22 @@
     <row r="42" ht="23" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>UDS-002</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Programming会话门禁</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
+          <t>UDS-018</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>F187双通道精确值读取</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>UDS</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>50 02 00 32 01 F4</t>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>62 F1 87 41 36 31 33 30 30 30 30 30 38 35 39 20</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -1158,22 +1318,22 @@
     <row r="43" ht="23" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>UDS-003</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Extended会话和P2/P2*</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
+          <t>UDS-019</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>F189双通道精确值读取</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>UDS</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>50 03 00 32 01 F4</t>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>62 F1 89 41 36 31 33 30 41 31 34 41 38 53 30 30 31 30 30 31</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -1185,22 +1345,22 @@
     <row r="44" ht="23" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>UDS-004</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>S3超时回Default</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
+          <t>UDS-020</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>F18A双通道精确值读取</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>UDS</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>S3超时后Boot已回到Default会话：7F 27 7E</t>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>62 F1 8A 41 31 34 34 38</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -1212,22 +1372,22 @@
     <row r="45" ht="23" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>UDS-005</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>TesterPresent和抑制正响应</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
+          <t>UDS-021</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>F191双通道精确值读取</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>UDS</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>在200ms观察窗内无响应</t>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>62 F1 91 41 36 31 33 30 41 31 34 34 38 48 30 30 31 30 30 31</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -1239,20 +1399,20 @@
     <row r="46" ht="23" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>UDS-007</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>系统标识DID读取</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
+          <t>UDS-022</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>F197双通道精确值读取</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>UDS</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>62 F1 97 46 41 4E 5F 46 20 20 20 20 20 20 20 20 20</t>
         </is>
@@ -1266,22 +1426,22 @@
     <row r="47" ht="23" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>UDS-018</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>F187双通道精确值读取</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
+          <t>UDS-008</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>DID写入门禁</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>UDS</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>62 F1 87 41 36 31 33 30 30 30 30 30 38 35 39 20</t>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>7F 2E 7F</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -1293,22 +1453,22 @@
     <row r="48" ht="23" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>UDS-019</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>F189双通道精确值读取</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
+          <t>UDS-009</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>DTC读取</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>UDS</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>62 F1 89 41 36 31 33 30 41 31 34 41 38 53 30 30 31 30 30 31</t>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>59 02 09</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -1320,22 +1480,22 @@
     <row r="49" ht="23" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>UDS-020</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>F18A双通道精确值读取</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
+          <t>UDS-012</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>不支持SID，NRC11</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>UDS</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>62 F1 8A 41 31 34 34 38</t>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>7F 99 11</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -1347,22 +1507,22 @@
     <row r="50" ht="23" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>UDS-021</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>F191双通道精确值读取</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
+          <t>UDS-013</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>不支持子功能，NRC12</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>UDS</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>62 F1 91 41 36 31 33 30 41 31 34 34 38 48 30 30 31 30 30 31</t>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>7F 10 12</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -1374,22 +1534,22 @@
     <row r="51" ht="23" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>UDS-022</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>F197双通道精确值读取</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
+          <t>UDS-014</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>长度错误，NRC13</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>UDS</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>62 F1 97 46 41 4E 5F 46 20 20 20 20 20 20 20 20 20</t>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>7F 10 13</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -1401,22 +1561,22 @@
     <row r="52" ht="23" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>UDS-008</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>DID写入门禁</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
+          <t>UDS-015</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>请求顺序错误，NRC24</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>UDS</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>7F 2E 7F</t>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>7F 36 24</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -1425,25 +1585,25 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="23" customHeight="1">
+    <row r="53" ht="38" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>UDS-009</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>DTC读取</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>UDS</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>59 02 09</t>
+          <t>SEC-001</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Level 1正确Key</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>安全访问</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Level 1解锁；Provider=FAN_F_Seed2Key_TEST_x64；SHA256=0e3596b4eb8f3...</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -1452,25 +1612,25 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="23" customHeight="1">
+    <row r="54" ht="38" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>UDS-012</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>不支持SID，NRC11</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>UDS</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>7F 99 11</t>
+          <t>SEC-002</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Level 3正确Key</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>安全访问</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Level 3解锁；Provider=FAN_F_Seed2Key_TEST_x64；SHA256=0e3596b4eb8f3...</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -1482,22 +1642,22 @@
     <row r="55" ht="23" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>UDS-013</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>不支持子功能，NRC12</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>UDS</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>7F 10 12</t>
+          <t>SEC-003</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>错误Key和NRC35</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>安全访问</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>7F 27 **REDACTED**</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -1509,22 +1669,22 @@
     <row r="56" ht="23" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>UDS-014</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>长度错误，NRC13</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>UDS</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>7F 10 13</t>
+          <t>SEC-004</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>无Seed直接发Key</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>安全访问</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>7F 27 **REDACTED**</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -1536,22 +1696,22 @@
     <row r="57" ht="23" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>UDS-015</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>请求顺序错误，NRC24</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>UDS</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>7F 36 24</t>
+          <t>SEC-008</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>会话降级清除权限</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>安全访问</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>7F 14 33</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -1560,25 +1720,25 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="38" customHeight="1">
+    <row r="58" ht="23" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>SEC-001</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Level 1正确Key</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>安全访问</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Level 1解锁；Provider=FAN_F_Seed2Key_TEST_x64；SHA256=0e3596b4eb8f3...</t>
+          <t>SYS-010</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>最终诊断与系统标识检查</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>系统检查</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>62 F1 97 46 41 4E 5F 46 20 20 20 20 20 20 20 20 20</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -1590,22 +1750,22 @@
     <row r="59" ht="38" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>SEC-002</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Level 3正确Key</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>安全访问</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Level 3解锁；Provider=FAN_F_Seed2Key_TEST_x64；SHA256=0e3596b4eb8f3...</t>
+          <t>UDS-006</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>ECUReset响应、复位和重连</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>UDS</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>ECU在第8次探测首次恢复；最终连续在线1500ms，复核4次；稳定窗口重启0次，复位/切换期间探测无响应7次（最终已恢复）</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -1617,22 +1777,22 @@
     <row r="60" ht="23" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>SEC-003</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>错误Key和NRC35</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>安全访问</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>7F 27 **REDACTED**</t>
+          <t>OTA-001</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>非编程会话RequestDownload</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>OTA</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>7F 34 7F</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -1641,25 +1801,25 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="23" customHeight="1">
+    <row r="61" ht="38" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>SEC-004</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>无Seed直接发Key</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>安全访问</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>7F 27 **REDACTED**</t>
+          <t>OTA-002</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>F002正常条件</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>OTA</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>OTA-002通过：正常边界：响应=71 01 F0 02 00，判定=允许；请求前条件快照已刷新；vehicle_speed...</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -1668,25 +1828,25 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="23" customHeight="1">
+    <row r="62" ht="38" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>SEC-008</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>会话降级清除权限</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>安全访问</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>7F 14 33</t>
+          <t>OTA-003</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>F002速度禁止</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>OTA</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>OTA-003通过：车速超限：响应=71 01 F0 02 01，判定=禁止；请求前条件快照已刷新；vehicle_speed...</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -1695,25 +1855,25 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="23" customHeight="1">
+    <row r="63" ht="38" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>SYS-010</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>最终诊断与系统标识检查</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>系统检查</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>62 F1 97 46 41 4E 5F 46 20 20 20 20 20 20 20 20 20</t>
+          <t>OTA-004</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>F002电源禁止</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>OTA</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>OTA-004通过：电源模式不满足：响应=71 01 F0 02 01，判定=禁止；请求前条件快照已刷新；vehicle_sp...</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -1725,22 +1885,22 @@
     <row r="64" ht="38" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>UDS-006</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>ECUReset响应、复位和重连</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>UDS</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>ECU在第8次探测首次恢复；最终连续在线1500ms，复核4次；稳定窗口重启0次，复位/切换期间探测无响应7次（最终已恢复）</t>
+          <t>OTA-005</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>F002驻车/发动机禁止</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>OTA</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>OTA-005通过：驻车条件不满足：响应=71 01 F0 02 01，判定=禁止；请求前条件快照已刷新；vehicle_sp...</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -1749,25 +1909,25 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="23" customHeight="1">
+    <row r="65" ht="38" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>OTA-001</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>非编程会话RequestDownload</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
+          <t>OTA-006</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>F002缺失/无效/超时策略</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>OTA</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>7F 34 7F</t>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>OTA-006通过：未接收：响应=71 01 F0 02 00，判定=允许；请求前条件快照已刷新；engine_speed帧龄...</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -1779,22 +1939,22 @@
     <row r="66" ht="38" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>OTA-002</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>F002正常条件</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
+          <t>OTA-007</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Flash Driver正常下载与认证</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>OTA</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>OTA-002通过：正常边界：响应=71 01 F0 02 00，判定=允许；请求前条件快照已刷新；vehicle_speed...</t>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>OTA-007 Flash Driver下载认证及F184 READY门禁通过，未发送FF00；Boot诊断F197在线</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -1806,22 +1966,22 @@
     <row r="67" ht="38" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>OTA-003</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>F002速度禁止</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
+          <t>OTA-010</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>合法RequestDownload与地址长度门禁</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>OTA</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>OTA-003通过：车速超限：响应=71 01 F0 02 01，判定=禁止；请求前条件快照已刷新；vehicle_speed...</t>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>OTA-010合法RequestDownload通过，错误地址、零长度和越界长度均被拒绝</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -1833,22 +1993,22 @@
     <row r="68" ht="38" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>OTA-004</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>F002电源禁止</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
+          <t>OTA-009</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>FF00擦除受控目标</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>OTA</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>OTA-004通过：电源模式不满足：响应=71 01 F0 02 01，判定=禁止；请求前条件快照已刷新；vehicle_sp...</t>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>OTA-009 FF00完成；未下载、未提交候选；复位后原可用运行态恢复：Boot诊断F197在线</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -1857,25 +2017,25 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="38" customHeight="1">
+    <row r="69" ht="23" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>OTA-005</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>F002驻车/发动机禁止</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
+          <t>OTA-028</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>正向完整在线升级</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>OTA</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>OTA-005通过：驻车条件不满足：响应=71 01 F0 02 01，判定=禁止；请求前条件快照已刷新；vehicle_sp...</t>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>ECU受控非活动区刷写、应用运行验证与Trial确认完成</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -1884,52 +2044,52 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="38" customHeight="1">
+    <row r="70" ht="23" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>OTA-006</t>
-        </is>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>F002缺失/无效/超时策略</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
+          <t>CAN-005</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>CAN周期</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>CAN/ISO-TP</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>count=5, min=483ms, max=541ms, expected=500±100ms</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="23" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>OTA-040</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>OBD/OTA安全隔离</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>OTA</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>OTA-006通过：未接收：响应=71 01 F0 02 00，判定=允许；请求前条件快照已刷新；engine_speed帧龄...</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="38" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>OTA-007</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Flash Driver正常下载与认证</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>OTA</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>OTA-007 Flash Driver下载认证及F184 READY门禁通过，未发送FF00；Boot诊断F197在线</t>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>7F 37 7F</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -1938,163 +2098,34 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="38" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>OTA-010</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>合法RequestDownload与地址长度门禁</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>OTA</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>OTA-010合法RequestDownload通过，错误地址、零长度和越界长度均被拒绝</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="38" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>OTA-009</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>FF00擦除受控目标</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>OTA</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>OTA-009 FF00完成；未下载、未提交候选；复位后原可用运行态恢复：Boot诊断F197在线</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="23" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>OTA-028</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>正向完整在线升级</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>OTA</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>ECU受控非活动区刷写、应用运行验证与Trial确认完成</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="23" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>CAN-005</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>CAN周期</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>CAN/ISO-TP</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>count=5, min=483ms, max=541ms, expected=500±100ms</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="23" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>OTA-040</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>OBD/OTA安全隔离</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>OTA</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>7F 37 7F</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="A33:E33"/>
+  <mergeCells count="24">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>